--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488136_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488136_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6463</v>
+        <v>9.2941</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4492</v>
+        <v>5.1462</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1971</v>
+        <v>4.1478</v>
       </c>
       <c r="G2" t="n">
         <v>10.0677</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2355</v>
+        <v>0.4122</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0943</v>
+        <v>-0.3973</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8588</v>
+        <v>0.8095</v>
       </c>
       <c r="V2" t="n">
         <v>-0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1314</v>
+        <v>6.6238</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1579</v>
+        <v>3.5271</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9735</v>
+        <v>3.0967</v>
       </c>
       <c r="G3" t="n">
         <v>5.1345</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8678</v>
+        <v>1.3601</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2473</v>
+        <v>0.6165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7436</v>
       </c>
       <c r="V3" t="n">
         <v>0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3678</v>
+        <v>6.2332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7285</v>
+        <v>0.4462</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6392</v>
+        <v>5.787</v>
       </c>
       <c r="G4" t="n">
         <v>2.1553</v>
@@ -766,13 +766,13 @@
         <v>3.1499</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9155</v>
+        <v>0.7809</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1567</v>
+        <v>-0.1256</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7588</v>
+        <v>0.9065</v>
       </c>
       <c r="V4" t="n">
         <v>1.2589</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9749</v>
+        <v>5.9317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0162</v>
+        <v>-0.027</v>
       </c>
       <c r="F5" t="n">
         <v>5.9586</v>
@@ -844,10 +844,10 @@
         <v>3.891</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2336</v>
+        <v>1.1904</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0621</v>
+        <v>-0.1054</v>
       </c>
       <c r="U5" t="n">
         <v>1.2957</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.7705</v>
+        <v>4.5658</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8683</v>
+        <v>0.9345</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9022</v>
+        <v>3.6314</v>
       </c>
       <c r="G6" t="n">
         <v>2.2554</v>
@@ -922,13 +922,13 @@
         <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1625</v>
+        <v>0.9578</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3867</v>
+        <v>-0.3205</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5492</v>
+        <v>1.2783</v>
       </c>
       <c r="V6" t="n">
         <v>-0.315</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1315</v>
+        <v>1.2205</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1206</v>
+        <v>-2.7734</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0109</v>
+        <v>3.9939</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5782</v>
+        <v>-0.8455</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0929</v>
+        <v>-0.3203</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4853</v>
+        <v>-0.5252</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1492</v>
+        <v>-1.2008</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2322</v>
+        <v>-0.6831</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>-0.5178</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.429</v>
+        <v>0.3553</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1393</v>
+        <v>0.3627</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5683</v>
+        <v>-0.0074</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>2.9646</v>
       </c>
       <c r="S7" t="n">
-        <v>1.58</v>
+        <v>0.8431</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1963</v>
+        <v>0.1691</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3837</v>
+        <v>0.674</v>
       </c>
       <c r="V7" t="n">
-        <v>0.315</v>
+        <v>-0.63</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X7" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.35</v>
+        <v>0.4947</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2745</v>
+        <v>-0.4669</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6246</v>
+        <v>0.9617</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8455</v>
+        <v>-0.5782</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3203</v>
+        <v>-0.0929</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5252</v>
+        <v>-0.4853</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2008</v>
+        <v>-0.1492</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6831</v>
+        <v>-0.2322</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5178</v>
+        <v>0.0829</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3553</v>
+        <v>-0.429</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3627</v>
+        <v>0.1393</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0074</v>
+        <v>-0.5683</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9646</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0274</v>
+        <v>0.9432</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.332</v>
+        <v>0.6087</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3046</v>
+        <v>0.3345</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.63</v>
+        <v>0.315</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0489</v>
+        <v>-0.3201</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5086</v>
+        <v>-4.0507</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4597</v>
+        <v>3.7306</v>
       </c>
       <c r="G10" t="n">
         <v>-2.658</v>
@@ -1234,13 +1234,13 @@
         <v>3.3352</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0383</v>
+        <v>0.6905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.0929</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.7834</v>
       </c>
       <c r="V10" t="n">
         <v>2.2033</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6804</v>
+        <v>-2.4918</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5009</v>
+        <v>-3.6968</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8205</v>
+        <v>1.205</v>
       </c>
       <c r="G11" t="n">
         <v>1.5929</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2647</v>
+        <v>0.4533</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2699</v>
+        <v>0.074</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9948</v>
+        <v>0.3793</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8061</v>
+        <v>-3.8941</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.631</v>
+        <v>-4.7928</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8249</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2245</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0813</v>
+        <v>0.8307</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7113</v>
+        <v>0.1269</v>
       </c>
       <c r="U12" t="n">
-        <v>0.63</v>
+        <v>0.7038</v>
       </c>
       <c r="V12" t="n">
         <v>-0.315</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>27.4811</v>
+        <v>28.3019</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.930200000000003</v>
+        <v>-5.109499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>33.4112</v>
+        <v>33.41139999999999</v>
       </c>
       <c r="G13" t="n">
         <v>19.2114</v>
@@ -1459,7 +1459,7 @@
         <v>2.4594</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.942890293094024e-16</v>
+        <v>2.498001805406602e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-24.0873</v>
@@ -1468,13 +1468,13 @@
         <v>24.0874</v>
       </c>
       <c r="S13" t="n">
-        <v>7.6416</v>
+        <v>8.462199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2671000000000002</v>
+        <v>0.5535000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>7.9087</v>
+        <v>7.908600000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.6283000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6474</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1094</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7568</v>
+        <v>0.8307</v>
       </c>
       <c r="G14" t="n">
         <v>0.6529</v>
@@ -1546,13 +1546,13 @@
         <v>0.1853</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1908</v>
+        <v>-0.1169</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4441</v>
+        <v>-0.427</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.75</v>
+        <v>-0.4714</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3058</v>
+        <v>0.0444</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0396</v>
+        <v>0.0683</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8339</v>
+        <v>0.6169</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2057</v>
+        <v>-0.5486</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2915</v>
+        <v>1.4082</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8199</v>
+        <v>2.0183</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5284</v>
+        <v>-0.6101</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3311</v>
+        <v>-1.3398</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6538</v>
+        <v>-1.4014</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3227</v>
+        <v>0.0616</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3352</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3355</v>
+        <v>-0.9221</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3357</v>
+        <v>-0.9532</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6712</v>
+        <v>0.0311</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6304999999999999</v>
+        <v>-0.3144</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6304999999999999</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8587</v>
+        <v>-0.9836</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5189</v>
+        <v>-4.1417</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6601</v>
+        <v>3.1581</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.5426</v>
+        <v>-1.0396</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.859</v>
+        <v>-0.8339</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3164</v>
+        <v>-0.2057</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9907</v>
+        <v>0.2915</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.178</v>
+        <v>0.8199</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1872</v>
+        <v>-0.5284</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5518</v>
+        <v>-1.3311</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.681</v>
+        <v>-1.6538</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1292</v>
+        <v>0.3227</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0382</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R18" t="n">
-        <v>3.891</v>
+        <v>3.3352</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4576</v>
+        <v>-0.2039</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6964</v>
+        <v>-0.7274</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2388</v>
+        <v>0.5235</v>
       </c>
       <c r="V18" t="n">
-        <v>0.188</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6283</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4403</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9676</v>
+        <v>-1.5642</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6673</v>
+        <v>-1.9691</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3003</v>
+        <v>0.4049</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0683</v>
+        <v>-1.5024</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6169</v>
+        <v>-1.716</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5486</v>
+        <v>0.2135</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4082</v>
+        <v>-1.1369</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0183</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6101</v>
+        <v>-0.5699</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3398</v>
+        <v>-0.3656</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4014</v>
+        <v>-1.149</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0616</v>
+        <v>0.7834</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4626</v>
+        <v>-0.2863</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.149</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3136</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5883</v>
+        <v>-2.0087</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.067</v>
+        <v>-3.7919</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4788</v>
+        <v>1.7832</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5024</v>
+        <v>-3.5426</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.716</v>
+        <v>-4.859</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2135</v>
+        <v>1.3164</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1369</v>
+        <v>-1.9907</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-2.178</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5699</v>
+        <v>0.1872</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3656</v>
+        <v>-1.5518</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.149</v>
+        <v>-2.681</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7834</v>
+        <v>1.1292</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>3.891</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3104</v>
+        <v>-0.6923</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9302</v>
+        <v>-0.5767</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6198</v>
+        <v>-0.1157</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2578</v>
+        <v>0.188</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6283</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2578</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0216</v>
+        <v>-2.0708</v>
       </c>
       <c r="E21" t="n">
         <v>-1.6058</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4158</v>
+        <v>-0.4651</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7823</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7951</v>
+        <v>-0.8444</v>
       </c>
       <c r="T21" t="n">
         <v>-0.383</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4121</v>
+        <v>-0.4614</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0024</v>
+        <v>-2.8329</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8263</v>
+        <v>-2.9232</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1761</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9541</v>
+        <v>-1.3352</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5517</v>
+        <v>-2.0862</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4024</v>
+        <v>0.751</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4226</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0644</v>
+        <v>-1.1984</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.487</v>
+        <v>0.6434</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5315</v>
+        <v>-0.7803</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6161</v>
+        <v>-0.8878</v>
       </c>
       <c r="O22" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9224</v>
+        <v>-0.6274</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5154</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3716</v>
+        <v>-0.1119</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1259</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1259</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2749</v>
+        <v>-3.1737</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1191</v>
+        <v>-3.0222</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1558</v>
+        <v>-0.1515</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3352</v>
+        <v>-1.9541</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0862</v>
+        <v>-1.5517</v>
       </c>
       <c r="I23" t="n">
-        <v>0.751</v>
+        <v>-0.4024</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4226</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1984</v>
+        <v>0.0644</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6434</v>
+        <v>-0.487</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7803</v>
+        <v>-1.5315</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8878</v>
+        <v>-1.6161</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1076</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0694</v>
+        <v>-1.0937</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7113</v>
+        <v>-0.7467</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3581</v>
+        <v>-0.347</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3144</v>
+        <v>-0.1259</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0203</v>
+        <v>-3.5071</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.735</v>
+        <v>-6.0495</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7147</v>
+        <v>2.5424</v>
       </c>
       <c r="G24" t="n">
         <v>0.1179</v>
@@ -2326,13 +2326,13 @@
         <v>4.0763</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6395</v>
+        <v>-1.1263</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.0244</v>
+        <v>-1.3389</v>
       </c>
       <c r="U24" t="n">
-        <v>0.385</v>
+        <v>0.2126</v>
       </c>
       <c r="V24" t="n">
         <v>1.7629</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8223</v>
+        <v>-4.6287</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4853</v>
+        <v>-3.8977</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.337</v>
+        <v>-0.7309</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6465</v>
@@ -2404,13 +2404,13 @@
         <v>3.3352</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3284</v>
+        <v>-1.1347</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8603</v>
+        <v>-1.2727</v>
       </c>
       <c r="U25" t="n">
-        <v>0.532</v>
+        <v>0.138</v>
       </c>
       <c r="V25" t="n">
         <v>-2.3297</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.0724</v>
+        <v>-7.9499</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4714</v>
+        <v>-6.3735</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.601</v>
+        <v>-1.5764</v>
       </c>
       <c r="G26" t="n">
         <v>-7.1918</v>
@@ -2482,13 +2482,13 @@
         <v>2.4087</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.716</v>
+        <v>-0.5935</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.4529</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1652</v>
+        <v>-0.1405</v>
       </c>
       <c r="V26" t="n">
         <v>1.1324</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.481</v>
+        <v>-27.4811</v>
       </c>
       <c r="E27" t="n">
-        <v>-33.4113</v>
+        <v>-33.4112</v>
       </c>
       <c r="F27" t="n">
-        <v>5.9302</v>
+        <v>5.930199999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-19.2112</v>
@@ -2533,7 +2533,7 @@
         <v>1.6506</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.392300000000001</v>
+        <v>-7.3923</v>
       </c>
       <c r="K27" t="n">
         <v>-4.9331</v>
@@ -2560,16 +2560,16 @@
         <v>24.0874</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.6415</v>
+        <v>-7.641500000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>-7.908700000000001</v>
+        <v>-7.908499999999998</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2673</v>
+        <v>0.2670999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.6284000000000001</v>
+        <v>-0.6283999999999998</v>
       </c>
       <c r="W27" t="n">
         <v>5.9771</v>
